--- a/analysis_results/noise/noise_summary_table.xlsx
+++ b/analysis_results/noise/noise_summary_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,42 +441,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>snr_9</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>snr_6</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>snr_3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>snr_0</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>snr_3</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>snr_6</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>snr_9</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>drop_snr_9</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>drop_snr_6</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_snr_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>drop_snr_0</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>drop_snr_3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>drop_snr_6</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>drop_snr_9</t>
         </is>
       </c>
     </row>
@@ -490,28 +490,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>0.9942987457240593</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9543899657924744</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7217787913340935</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.4139110604332953</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.7217787913340935</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.9543899657924744</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9942987457240593</v>
-      </c>
       <c r="G2" t="n">
+        <v>0.5701254275940704</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.561003420752563</v>
+      </c>
+      <c r="I2" t="n">
+        <v>27.82212086659065</v>
+      </c>
+      <c r="J2" t="n">
         <v>58.60889395667046</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27.82212086659065</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.561003420752563</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5701254275940704</v>
       </c>
     </row>
     <row r="3">
@@ -524,28 +524,28 @@
         <v>0.9965792474344356</v>
       </c>
       <c r="C3" t="n">
+        <v>0.9942987457240593</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.992018244013683</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9863169897377423</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.942987457240593</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.9863169897377423</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.992018244013683</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9942987457240593</v>
-      </c>
       <c r="G3" t="n">
+        <v>0.2288329519450822</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4576659038901644</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.029748283752864</v>
+      </c>
+      <c r="J3" t="n">
         <v>5.377574370709381</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.029748283752864</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.4576659038901644</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.2288329519450822</v>
       </c>
     </row>
     <row r="4">
@@ -558,28 +558,28 @@
         <v>0.9942987457240593</v>
       </c>
       <c r="C4" t="n">
+        <v>0.9783352337514253</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9338654503990877</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7559863169897377</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.4481185860889396</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.7559863169897377</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9338654503990877</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9783352337514253</v>
-      </c>
       <c r="G4" t="n">
+        <v>1.605504587155967</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.077981651376152</v>
+      </c>
+      <c r="I4" t="n">
+        <v>23.96788990825688</v>
+      </c>
+      <c r="J4" t="n">
         <v>54.93119266055045</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.96788990825688</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6.077981651376152</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.605504587155967</v>
       </c>
     </row>
     <row r="5">
@@ -592,28 +592,28 @@
         <v>0.9965792474344356</v>
       </c>
       <c r="C5" t="n">
+        <v>0.9703534777651083</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9258836944127709</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7924743443557583</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.5507411630558723</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.7924743443557583</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9258836944127709</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9703534777651083</v>
-      </c>
       <c r="G5" t="n">
+        <v>2.631578947368428</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7.093821510297481</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20.48054919908467</v>
+      </c>
+      <c r="J5" t="n">
         <v>44.73684210526316</v>
-      </c>
-      <c r="H5" t="n">
-        <v>20.48054919908467</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7.093821510297481</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.631578947368428</v>
       </c>
     </row>
     <row r="6">
@@ -626,28 +626,28 @@
         <v>0.9646522234891676</v>
       </c>
       <c r="C6" t="n">
+        <v>0.9201824401368301</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8358038768529077</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6659064994298746</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.4241733181299886</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.6659064994298746</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8358038768529077</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9201824401368301</v>
-      </c>
       <c r="G6" t="n">
+        <v>4.609929078014175</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13.35697399527186</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30.9692671394799</v>
+      </c>
+      <c r="J6" t="n">
         <v>56.02836879432624</v>
-      </c>
-      <c r="H6" t="n">
-        <v>30.9692671394799</v>
-      </c>
-      <c r="I6" t="n">
-        <v>13.35697399527186</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.609929078014175</v>
       </c>
     </row>
     <row r="7">
@@ -660,28 +660,62 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
+        <v>0.9589509692132269</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7297605473204105</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4218928164196123</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.314709236031927</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.4218928164196123</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.7297605473204105</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.9589509692132269</v>
-      </c>
       <c r="G7" t="n">
+        <v>4.104903078677314</v>
+      </c>
+      <c r="H7" t="n">
+        <v>27.02394526795895</v>
+      </c>
+      <c r="I7" t="n">
+        <v>57.81071835803877</v>
+      </c>
+      <c r="J7" t="n">
         <v>68.5290763968073</v>
       </c>
-      <c r="H7" t="n">
-        <v>57.81071835803877</v>
-      </c>
-      <c r="I7" t="n">
-        <v>27.02394526795895</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.104903078677314</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>cnn_transformer_noiseaug</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9988597491448119</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9977194982896237</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.984036488027366</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8768529076396807</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.114155251141548</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1141552511415591</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.484018264840191</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12.21461187214613</v>
       </c>
     </row>
   </sheetData>
